--- a/Dados_brutos/octoprint_print_history_export.xlsx
+++ b/Dados_brutos/octoprint_print_history_export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="1024">
   <si>
     <t>File name</t>
   </si>
@@ -2606,6 +2606,486 @@
   </si>
   <si>
     <t>1:04:38</t>
+  </si>
+  <si>
+    <t>2025-03-31 17:33:49</t>
+  </si>
+  <si>
+    <t>0:56:44</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.3_Den_5%_Noz_0.4_Tim_014756.gcode</t>
+  </si>
+  <si>
+    <t>2025-03-31 20:00:15</t>
+  </si>
+  <si>
+    <t>1:55:24</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.4_Den_5%_Noz_0.4_Tim_002120.gcode</t>
+  </si>
+  <si>
+    <t>2025-03-31 23:03:24</t>
+  </si>
+  <si>
+    <t>0:22:38</t>
+  </si>
+  <si>
+    <t>PLA_Octopus_spiral_sup_v6_Res_0.1_Den_5%_Noz_0.4_Tim_071256.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 06:26:17</t>
+  </si>
+  <si>
+    <t>7:19:33</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.1_Den_5%_Noz_0.4_Tim_005443.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 09:33:30</t>
+  </si>
+  <si>
+    <t>0:58:49</t>
+  </si>
+  <si>
+    <t>PLA_3D_Printer_test_fixed_stl_3rd_gen_Res_0.1_Den_25%_Noz_0.4_Tim_043639.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 10:55:50</t>
+  </si>
+  <si>
+    <t>0:38:47</t>
+  </si>
+  <si>
+    <t>2025-04-01 13:08:33</t>
+  </si>
+  <si>
+    <t>2:12:06</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.3_Den_5%_Noz_0.4_Tim_002516.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 20:50:37</t>
+  </si>
+  <si>
+    <t>0:26:35</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.3_Den_5%_Noz_0.4_Tim_004941.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 22:22:30</t>
+  </si>
+  <si>
+    <t>0:53:44</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.2_Den_5%_Noz_0.4_Tim_003204.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-01 23:36:40</t>
+  </si>
+  <si>
+    <t>0:36:09</t>
+  </si>
+  <si>
+    <t>PLA_Ball_Bearing.A.3_Res_0.1_Den_5%_Noz_0.4_Tim_064647.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-02 08:10:45</t>
+  </si>
+  <si>
+    <t>6:50:20</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.1_Den_5%_Noz_0.4_Tim_020044.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-02 17:34:57</t>
+  </si>
+  <si>
+    <t>2025-04-02 19:40:13</t>
+  </si>
+  <si>
+    <t>0:05:32</t>
+  </si>
+  <si>
+    <t>2025-04-02 19:43:47</t>
+  </si>
+  <si>
+    <t>0:03:28</t>
+  </si>
+  <si>
+    <t>2025-04-02 19:46:54</t>
+  </si>
+  <si>
+    <t>0:02:57</t>
+  </si>
+  <si>
+    <t>2025-04-02 19:48:42</t>
+  </si>
+  <si>
+    <t>2025-04-02 19:50:38</t>
+  </si>
+  <si>
+    <t>0:01:46</t>
+  </si>
+  <si>
+    <t>2025-04-02 20:09:17</t>
+  </si>
+  <si>
+    <t>0:18:24</t>
+  </si>
+  <si>
+    <t>2025-04-02 22:14:30</t>
+  </si>
+  <si>
+    <t>2:03:43</t>
+  </si>
+  <si>
+    <t>2025-04-03 00:46:32</t>
+  </si>
+  <si>
+    <t>2:15:32</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.1_Den_5%_Noz_0.4_Tim_044102.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-03 00:53:14</t>
+  </si>
+  <si>
+    <t>0:05:31</t>
+  </si>
+  <si>
+    <t>2025-04-03 05:33:22</t>
+  </si>
+  <si>
+    <t>4:39:59</t>
+  </si>
+  <si>
+    <t>2025-04-03 17:01:03</t>
+  </si>
+  <si>
+    <t>1:15:07</t>
+  </si>
+  <si>
+    <t>PLA_3D_Printer_test_fixed_stl_3rd_gen_Res_0.1_Den_15%_Noz_0.4_Tim_113600.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-04 06:41:06</t>
+  </si>
+  <si>
+    <t>11:36:49</t>
+  </si>
+  <si>
+    <t>PLA_peristaltic_Res_0.1_Den_5%_Noz_0.4_Tim_051406.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-04 20:25:34</t>
+  </si>
+  <si>
+    <t>0:09:21</t>
+  </si>
+  <si>
+    <t>PLA_peristaltic_Res_0.1_Den_5%_Noz_0.4_Tim_051403.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-04 21:09:34</t>
+  </si>
+  <si>
+    <t>0:38:21</t>
+  </si>
+  <si>
+    <t>2025-04-05 02:35:38</t>
+  </si>
+  <si>
+    <t>5:18:59</t>
+  </si>
+  <si>
+    <t>2025-04-05 08:24:25</t>
+  </si>
+  <si>
+    <t>5:16:54</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.1_Den_5%_Noz_0.4_Tim_043752.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-05 13:18:17</t>
+  </si>
+  <si>
+    <t>4:30:28</t>
+  </si>
+  <si>
+    <t>PLA_wildrosebuilds_puzzlecube_Res_0.1_Den_5%_Noz_0.4_Tim_051116.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-05 19:03:37</t>
+  </si>
+  <si>
+    <t>5:13:48</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.1_Den_5%_Noz_0.4_Tim_044056.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 02:20:54</t>
+  </si>
+  <si>
+    <t>4:07:56</t>
+  </si>
+  <si>
+    <t>2025-04-06 07:22:56</t>
+  </si>
+  <si>
+    <t>4:40:41</t>
+  </si>
+  <si>
+    <t>2025-04-06 16:20:19</t>
+  </si>
+  <si>
+    <t>0:21:11</t>
+  </si>
+  <si>
+    <t>2025-04-06 21:01:43</t>
+  </si>
+  <si>
+    <t>4:40:40</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.4_Den_5%_Noz_1.0_Tim_001111.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 21:31:12</t>
+  </si>
+  <si>
+    <t>0:00:11</t>
+  </si>
+  <si>
+    <t>2025-04-06 21:53:47</t>
+  </si>
+  <si>
+    <t>0:15:04</t>
+  </si>
+  <si>
+    <t>2025-04-06 22:11:35</t>
+  </si>
+  <si>
+    <t>2025-04-06 22:17:45</t>
+  </si>
+  <si>
+    <t>2025-04-06 22:21:03</t>
+  </si>
+  <si>
+    <t>0:03:16</t>
+  </si>
+  <si>
+    <t>2025-04-06 22:36:56</t>
+  </si>
+  <si>
+    <t>0:13:16</t>
+  </si>
+  <si>
+    <t>2025-04-06 22:52:42</t>
+  </si>
+  <si>
+    <t>0:14:51</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.8_Den_5%_Noz_1.0_Tim_000614.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 23:05:02</t>
+  </si>
+  <si>
+    <t>0:10:11</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.4_Den_5%_Noz_1.0_Tim_001023.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 23:20:30</t>
+  </si>
+  <si>
+    <t>0:14:11</t>
+  </si>
+  <si>
+    <t>PLA_xyzCalibration_cube_Res_0.8_Den_5%_Noz_1.0_Tim_000639.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 23:32:14</t>
+  </si>
+  <si>
+    <t>0:10:25</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.8_Den_5%_Noz_1.0_Tim_001231.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 23:38:49</t>
+  </si>
+  <si>
+    <t>0:05:04</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.8_Den_5%_Noz_1.0_Tim_001127.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-06 23:47:14</t>
+  </si>
+  <si>
+    <t>0:04:19</t>
+  </si>
+  <si>
+    <t>2025-04-07 00:01:59</t>
+  </si>
+  <si>
+    <t>0:14:34</t>
+  </si>
+  <si>
+    <t>2025-04-07 00:17:32</t>
+  </si>
+  <si>
+    <t>0:15:12</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.1_Den_5%_Noz_1.0_Tim_043253.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 04:48:25</t>
+  </si>
+  <si>
+    <t>4:29:40</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.8_Den_5%_Noz_1.0_Tim_004519.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 05:56:59</t>
+  </si>
+  <si>
+    <t>0:44:23</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.1_Den_5%_Noz_1.0_Tim_010744.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 14:07:44</t>
+  </si>
+  <si>
+    <t>0:17:09</t>
+  </si>
+  <si>
+    <t>2025-04-07 15:20:21</t>
+  </si>
+  <si>
+    <t>1:12:03</t>
+  </si>
+  <si>
+    <t>PLA_Ball_Bearing.A.3_Res_0.4_Den_5%_Noz_1.0_Tim_010845.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 16:36:50</t>
+  </si>
+  <si>
+    <t>1:11:14</t>
+  </si>
+  <si>
+    <t>PLA_wildrosebuilds_puzzlecube_Res_0.8_Den_5%_Noz_1.0_Tim_005933.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 19:02:49</t>
+  </si>
+  <si>
+    <t>0:59:33</t>
+  </si>
+  <si>
+    <t>PLA_peristaltic_Res_0.8_Den_5%_Noz_1.0_Tim_003703.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 19:43:46</t>
+  </si>
+  <si>
+    <t>0:36:42</t>
+  </si>
+  <si>
+    <t>2025-04-07 20:27:37</t>
+  </si>
+  <si>
+    <t>0:36:52</t>
+  </si>
+  <si>
+    <t>PLA_Octopus_spiral_sup_v6_Res_0.1_Den_5%_Noz_1.0_Tim_041942.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-07 22:56:37</t>
+  </si>
+  <si>
+    <t>0:14:07</t>
+  </si>
+  <si>
+    <t>2025-04-08 00:01:51</t>
+  </si>
+  <si>
+    <t>1:04:24</t>
+  </si>
+  <si>
+    <t>2025-04-08 00:32:43</t>
+  </si>
+  <si>
+    <t>0:30:14</t>
+  </si>
+  <si>
+    <t>PLA_3D_Printer_test_fixed_stl_3rd_gen_Res_0.4_Den_20%_Noz_1.0_Tim_011637.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-08 00:39:18</t>
+  </si>
+  <si>
+    <t>0:05:57</t>
+  </si>
+  <si>
+    <t>PLA_3D_Printer_test_fixed_stl_3rd_gen_Res_0.4_Den_20%_Noz_1.0_Tim_014949.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-08 02:03:44</t>
+  </si>
+  <si>
+    <t>1:22:21</t>
+  </si>
+  <si>
+    <t>2025-04-08 04:11:51</t>
+  </si>
+  <si>
+    <t>2:07:25</t>
+  </si>
+  <si>
+    <t>PLA_peristaltic_Res_0.4_Den_5%_Noz_1.0_Tim_005754.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-08 06:53:01</t>
+  </si>
+  <si>
+    <t>1:10:06</t>
+  </si>
+  <si>
+    <t>PLA_peristaltic_Res_0.1_Den_5%_Noz_1.0_Tim_025114.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-08 09:04:07</t>
+  </si>
+  <si>
+    <t>0:08:35</t>
+  </si>
+  <si>
+    <t>2025-04-08 12:26:34</t>
+  </si>
+  <si>
+    <t>3:22:22</t>
   </si>
 </sst>
 </file>
@@ -2937,7 +3417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H446"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10566,6 +11046,1306 @@
         <v>0</v>
       </c>
     </row>
+    <row r="382" spans="1:7">
+      <c r="A382" t="s">
+        <v>861</v>
+      </c>
+      <c r="B382" t="s">
+        <v>864</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382" t="s">
+        <v>865</v>
+      </c>
+      <c r="F382">
+        <v>6870.260299999875</v>
+      </c>
+      <c r="G382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" t="s">
+        <v>866</v>
+      </c>
+      <c r="B383" t="s">
+        <v>867</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383" t="s">
+        <v>868</v>
+      </c>
+      <c r="F383">
+        <v>0</v>
+      </c>
+      <c r="G383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" t="s">
+        <v>869</v>
+      </c>
+      <c r="B384" t="s">
+        <v>870</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384" t="s">
+        <v>871</v>
+      </c>
+      <c r="F384">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" t="s">
+        <v>872</v>
+      </c>
+      <c r="B385" t="s">
+        <v>873</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+      <c r="D385" t="s">
+        <v>874</v>
+      </c>
+      <c r="F385">
+        <v>7462.375519999778</v>
+      </c>
+      <c r="G385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" t="s">
+        <v>875</v>
+      </c>
+      <c r="B386" t="s">
+        <v>876</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>877</v>
+      </c>
+      <c r="F386">
+        <v>1133.135790000001</v>
+      </c>
+      <c r="G386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" t="s">
+        <v>878</v>
+      </c>
+      <c r="B387" t="s">
+        <v>879</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387" t="s">
+        <v>880</v>
+      </c>
+      <c r="F387">
+        <v>4306.397529999959</v>
+      </c>
+      <c r="G387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" t="s">
+        <v>878</v>
+      </c>
+      <c r="B388" t="s">
+        <v>881</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388" t="s">
+        <v>882</v>
+      </c>
+      <c r="F388">
+        <v>4306.397529999959</v>
+      </c>
+      <c r="G388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" t="s">
+        <v>883</v>
+      </c>
+      <c r="B389" t="s">
+        <v>884</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>885</v>
+      </c>
+      <c r="F389">
+        <v>1398.841559999999</v>
+      </c>
+      <c r="G389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" t="s">
+        <v>886</v>
+      </c>
+      <c r="B390" t="s">
+        <v>887</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>888</v>
+      </c>
+      <c r="F390">
+        <v>2587.597799999998</v>
+      </c>
+      <c r="G390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" t="s">
+        <v>889</v>
+      </c>
+      <c r="B391" t="s">
+        <v>890</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>891</v>
+      </c>
+      <c r="F391">
+        <v>1249.57566</v>
+      </c>
+      <c r="G391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
+        <v>892</v>
+      </c>
+      <c r="B392" t="s">
+        <v>893</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>894</v>
+      </c>
+      <c r="F392">
+        <v>8168.369249999778</v>
+      </c>
+      <c r="G392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" t="s">
+        <v>895</v>
+      </c>
+      <c r="B393" t="s">
+        <v>896</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393" t="s">
+        <v>192</v>
+      </c>
+      <c r="F393">
+        <v>2270.318910000004</v>
+      </c>
+      <c r="G393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" t="s">
+        <v>869</v>
+      </c>
+      <c r="B394" t="s">
+        <v>897</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394" t="s">
+        <v>898</v>
+      </c>
+      <c r="F394">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" t="s">
+        <v>869</v>
+      </c>
+      <c r="B395" t="s">
+        <v>899</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395" t="s">
+        <v>900</v>
+      </c>
+      <c r="F395">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" t="s">
+        <v>869</v>
+      </c>
+      <c r="B396" t="s">
+        <v>901</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396" t="s">
+        <v>902</v>
+      </c>
+      <c r="F396">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" t="s">
+        <v>869</v>
+      </c>
+      <c r="B397" t="s">
+        <v>903</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397" t="s">
+        <v>104</v>
+      </c>
+      <c r="F397">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" t="s">
+        <v>869</v>
+      </c>
+      <c r="B398" t="s">
+        <v>904</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398" t="s">
+        <v>905</v>
+      </c>
+      <c r="F398">
+        <v>1530.111760000001</v>
+      </c>
+      <c r="G398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" t="s">
+        <v>895</v>
+      </c>
+      <c r="B399" t="s">
+        <v>906</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399" t="s">
+        <v>907</v>
+      </c>
+      <c r="F399">
+        <v>2270.318910000004</v>
+      </c>
+      <c r="G399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" t="s">
+        <v>895</v>
+      </c>
+      <c r="B400" t="s">
+        <v>908</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>909</v>
+      </c>
+      <c r="F400">
+        <v>2270.318910000004</v>
+      </c>
+      <c r="G400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" t="s">
+        <v>878</v>
+      </c>
+      <c r="B401" t="s">
+        <v>910</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401" t="s">
+        <v>911</v>
+      </c>
+      <c r="F401">
+        <v>4306.397529999959</v>
+      </c>
+      <c r="G401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" t="s">
+        <v>912</v>
+      </c>
+      <c r="B402" t="s">
+        <v>913</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402" t="s">
+        <v>914</v>
+      </c>
+      <c r="F402">
+        <v>6400.447369999823</v>
+      </c>
+      <c r="G402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" t="s">
+        <v>912</v>
+      </c>
+      <c r="B403" t="s">
+        <v>915</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>916</v>
+      </c>
+      <c r="F403">
+        <v>6400.447369999823</v>
+      </c>
+      <c r="G403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" t="s">
+        <v>878</v>
+      </c>
+      <c r="B404" t="s">
+        <v>917</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404" t="s">
+        <v>918</v>
+      </c>
+      <c r="F404">
+        <v>4306.397529999959</v>
+      </c>
+      <c r="G404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" t="s">
+        <v>919</v>
+      </c>
+      <c r="B405" t="s">
+        <v>920</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>921</v>
+      </c>
+      <c r="F405">
+        <v>12517.56360000196</v>
+      </c>
+      <c r="G405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" t="s">
+        <v>922</v>
+      </c>
+      <c r="B406" t="s">
+        <v>923</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406" t="s">
+        <v>924</v>
+      </c>
+      <c r="F406">
+        <v>5913.011970000144</v>
+      </c>
+      <c r="G406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" t="s">
+        <v>925</v>
+      </c>
+      <c r="B407" t="s">
+        <v>926</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407" t="s">
+        <v>927</v>
+      </c>
+      <c r="F407">
+        <v>0</v>
+      </c>
+      <c r="G407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" t="s">
+        <v>925</v>
+      </c>
+      <c r="B408" t="s">
+        <v>928</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>929</v>
+      </c>
+      <c r="F408">
+        <v>5913.989420000054</v>
+      </c>
+      <c r="G408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" t="s">
+        <v>925</v>
+      </c>
+      <c r="B409" t="s">
+        <v>930</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" t="s">
+        <v>931</v>
+      </c>
+      <c r="F409">
+        <v>5913.989420000054</v>
+      </c>
+      <c r="G409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7">
+      <c r="A410" t="s">
+        <v>932</v>
+      </c>
+      <c r="B410" t="s">
+        <v>933</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410" t="s">
+        <v>934</v>
+      </c>
+      <c r="F410">
+        <v>6601.621509999644</v>
+      </c>
+      <c r="G410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7">
+      <c r="A411" t="s">
+        <v>935</v>
+      </c>
+      <c r="B411" t="s">
+        <v>936</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" t="s">
+        <v>937</v>
+      </c>
+      <c r="F411">
+        <v>0</v>
+      </c>
+      <c r="G411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412" t="s">
+        <v>938</v>
+      </c>
+      <c r="B412" t="s">
+        <v>939</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412" t="s">
+        <v>940</v>
+      </c>
+      <c r="F412">
+        <v>6588.47002999985</v>
+      </c>
+      <c r="G412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7">
+      <c r="A413" t="s">
+        <v>938</v>
+      </c>
+      <c r="B413" t="s">
+        <v>941</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="s">
+        <v>942</v>
+      </c>
+      <c r="F413">
+        <v>6588.47002999985</v>
+      </c>
+      <c r="G413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
+      <c r="A414" t="s">
+        <v>938</v>
+      </c>
+      <c r="B414" t="s">
+        <v>943</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414" t="s">
+        <v>944</v>
+      </c>
+      <c r="F414">
+        <v>6588.47002999985</v>
+      </c>
+      <c r="G414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415" t="s">
+        <v>938</v>
+      </c>
+      <c r="B415" t="s">
+        <v>945</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+      <c r="D415" t="s">
+        <v>946</v>
+      </c>
+      <c r="F415">
+        <v>6588.47002999985</v>
+      </c>
+      <c r="G415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
+      <c r="A416" t="s">
+        <v>947</v>
+      </c>
+      <c r="B416" t="s">
+        <v>948</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+      <c r="D416" t="s">
+        <v>949</v>
+      </c>
+      <c r="F416">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7">
+      <c r="A417" t="s">
+        <v>947</v>
+      </c>
+      <c r="B417" t="s">
+        <v>950</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" t="s">
+        <v>951</v>
+      </c>
+      <c r="F417">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
+      <c r="A418" t="s">
+        <v>947</v>
+      </c>
+      <c r="B418" t="s">
+        <v>952</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418" t="s">
+        <v>186</v>
+      </c>
+      <c r="F418">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7">
+      <c r="A419" t="s">
+        <v>947</v>
+      </c>
+      <c r="B419" t="s">
+        <v>953</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419" t="s">
+        <v>264</v>
+      </c>
+      <c r="F419">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7">
+      <c r="A420" t="s">
+        <v>947</v>
+      </c>
+      <c r="B420" t="s">
+        <v>954</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420" t="s">
+        <v>955</v>
+      </c>
+      <c r="F420">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7">
+      <c r="A421" t="s">
+        <v>947</v>
+      </c>
+      <c r="B421" t="s">
+        <v>956</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+      <c r="D421" t="s">
+        <v>957</v>
+      </c>
+      <c r="F421">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7">
+      <c r="A422" t="s">
+        <v>947</v>
+      </c>
+      <c r="B422" t="s">
+        <v>958</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422" t="s">
+        <v>959</v>
+      </c>
+      <c r="F422">
+        <v>1637.491859999998</v>
+      </c>
+      <c r="G422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7">
+      <c r="A423" t="s">
+        <v>960</v>
+      </c>
+      <c r="B423" t="s">
+        <v>961</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>962</v>
+      </c>
+      <c r="F423">
+        <v>1349.10303</v>
+      </c>
+      <c r="G423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7">
+      <c r="A424" t="s">
+        <v>963</v>
+      </c>
+      <c r="B424" t="s">
+        <v>964</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424" t="s">
+        <v>965</v>
+      </c>
+      <c r="F424">
+        <v>1117.55159</v>
+      </c>
+      <c r="G424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7">
+      <c r="A425" t="s">
+        <v>966</v>
+      </c>
+      <c r="B425" t="s">
+        <v>967</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425" t="s">
+        <v>968</v>
+      </c>
+      <c r="F425">
+        <v>1940.971770000001</v>
+      </c>
+      <c r="G425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7">
+      <c r="A426" t="s">
+        <v>969</v>
+      </c>
+      <c r="B426" t="s">
+        <v>970</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426" t="s">
+        <v>971</v>
+      </c>
+      <c r="F426">
+        <v>0</v>
+      </c>
+      <c r="G426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7">
+      <c r="A427" t="s">
+        <v>972</v>
+      </c>
+      <c r="B427" t="s">
+        <v>973</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427" t="s">
+        <v>974</v>
+      </c>
+      <c r="F427">
+        <v>3334.705569999997</v>
+      </c>
+      <c r="G427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" t="s">
+        <v>972</v>
+      </c>
+      <c r="B428" t="s">
+        <v>975</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428" t="s">
+        <v>976</v>
+      </c>
+      <c r="F428">
+        <v>3334.705569999997</v>
+      </c>
+      <c r="G428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" t="s">
+        <v>972</v>
+      </c>
+      <c r="B429" t="s">
+        <v>977</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
+      <c r="D429" t="s">
+        <v>978</v>
+      </c>
+      <c r="F429">
+        <v>3334.705569999997</v>
+      </c>
+      <c r="G429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7">
+      <c r="A430" t="s">
+        <v>979</v>
+      </c>
+      <c r="B430" t="s">
+        <v>980</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>981</v>
+      </c>
+      <c r="F430">
+        <v>15330.37602999979</v>
+      </c>
+      <c r="G430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7">
+      <c r="A431" t="s">
+        <v>982</v>
+      </c>
+      <c r="B431" t="s">
+        <v>983</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431" t="s">
+        <v>984</v>
+      </c>
+      <c r="F431">
+        <v>16726.29184000004</v>
+      </c>
+      <c r="G431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7">
+      <c r="A432" t="s">
+        <v>985</v>
+      </c>
+      <c r="B432" t="s">
+        <v>986</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432" t="s">
+        <v>987</v>
+      </c>
+      <c r="F432">
+        <v>0</v>
+      </c>
+      <c r="G432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7">
+      <c r="A433" t="s">
+        <v>985</v>
+      </c>
+      <c r="B433" t="s">
+        <v>988</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433" t="s">
+        <v>989</v>
+      </c>
+      <c r="F433">
+        <v>2948.22129000001</v>
+      </c>
+      <c r="G433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7">
+      <c r="A434" t="s">
+        <v>990</v>
+      </c>
+      <c r="B434" t="s">
+        <v>991</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434" t="s">
+        <v>992</v>
+      </c>
+      <c r="F434">
+        <v>12388.75366000007</v>
+      </c>
+      <c r="G434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7">
+      <c r="A435" t="s">
+        <v>993</v>
+      </c>
+      <c r="B435" t="s">
+        <v>994</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435" t="s">
+        <v>995</v>
+      </c>
+      <c r="F435">
+        <v>20821.46515000002</v>
+      </c>
+      <c r="G435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7">
+      <c r="A436" t="s">
+        <v>996</v>
+      </c>
+      <c r="B436" t="s">
+        <v>997</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436" t="s">
+        <v>998</v>
+      </c>
+      <c r="F436">
+        <v>13172.98950000005</v>
+      </c>
+      <c r="G436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7">
+      <c r="A437" t="s">
+        <v>996</v>
+      </c>
+      <c r="B437" t="s">
+        <v>999</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F437">
+        <v>13172.98950000005</v>
+      </c>
+      <c r="G437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
+      <c r="A438" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F438">
+        <v>0</v>
+      </c>
+      <c r="G438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7">
+      <c r="A439" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F439">
+        <v>7995.726780000092</v>
+      </c>
+      <c r="G439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
+      <c r="A440" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F440">
+        <v>7995.726780000092</v>
+      </c>
+      <c r="G440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
+      <c r="A441" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F441">
+        <v>15874.62881999987</v>
+      </c>
+      <c r="G441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7">
+      <c r="A442" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F442">
+        <v>15295.78720000044</v>
+      </c>
+      <c r="G442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7">
+      <c r="A443" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+      <c r="D443" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F443">
+        <v>15295.78720000044</v>
+      </c>
+      <c r="G443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7">
+      <c r="A444" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+      <c r="D444" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F444">
+        <v>10212.18148999999</v>
+      </c>
+      <c r="G444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7">
+      <c r="A445" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F445">
+        <v>7664.273250000223</v>
+      </c>
+      <c r="G445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F446">
+        <v>7664.273250000223</v>
+      </c>
+      <c r="G446">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Dados_brutos/octoprint_print_history_export.xlsx
+++ b/Dados_brutos/octoprint_print_history_export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1259">
   <si>
     <t>File name</t>
   </si>
@@ -3086,6 +3086,711 @@
   </si>
   <si>
     <t>3:22:22</t>
+  </si>
+  <si>
+    <t>PLA_wildrosebuilds_puzzlecube_Res_0.4_Den_5%_Noz_1.0_Tim_012854.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-09 04:28:31</t>
+  </si>
+  <si>
+    <t>1:44:39</t>
+  </si>
+  <si>
+    <t>PLA_Ball_Bearing.A.3_Res_0.8_Den_5%_Noz_1.0_Tim_003902.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-09 15:20:28</t>
+  </si>
+  <si>
+    <t>0:47:43</t>
+  </si>
+  <si>
+    <t>2025-04-09 16:50:23</t>
+  </si>
+  <si>
+    <t>0:00:02</t>
+  </si>
+  <si>
+    <t>PLA_Octopus_spiral_sup_v6_Res_0.1_Den_5%_Noz_1.0_Tim_043132.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-09 22:15:57</t>
+  </si>
+  <si>
+    <t>5:18:49</t>
+  </si>
+  <si>
+    <t>PLA_Octopus_spiral_sup_v6_Res_0.8_Den_5%_Noz_1.0_Tim_005110.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-13 16:13:42</t>
+  </si>
+  <si>
+    <t>0:53:54</t>
+  </si>
+  <si>
+    <t>PLA_Octopus_spiral_sup_v6_Res_0.5_Den_5%_Noz_1.0_Tim_010821.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-13 17:44:37</t>
+  </si>
+  <si>
+    <t>1:12:43</t>
+  </si>
+  <si>
+    <t>PLA_sharkz_Res_0.5_Den_5%_Noz_1.0_Tim_001555.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-13 18:49:05</t>
+  </si>
+  <si>
+    <t>0:21:05</t>
+  </si>
+  <si>
+    <t>PLA_VaseDoubleTwist_Res_0.5_Den_5%_Noz_1.0_Tim_010257.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-13 19:52:39</t>
+  </si>
+  <si>
+    <t>1:01:48</t>
+  </si>
+  <si>
+    <t>PLA_Ball_Bearing.A.3_Res_0.1_Den_5%_Noz_1.0_Tim_040912.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-13 20:38:59</t>
+  </si>
+  <si>
+    <t>0:42:00</t>
+  </si>
+  <si>
+    <t>2025-04-14 00:27:29</t>
+  </si>
+  <si>
+    <t>3:47:53</t>
+  </si>
+  <si>
+    <t>PLA_wildrosebuilds_puzzlecube_Res_0.1_Den_5%_Noz_1.0_Tim_042202.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 04:52:39</t>
+  </si>
+  <si>
+    <t>4:24:09</t>
+  </si>
+  <si>
+    <t>2025-04-14 12:45:07</t>
+  </si>
+  <si>
+    <t>0:13:21</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.5_Den_10%_Noz_1.0_Tim_000922.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 13:54:21</t>
+  </si>
+  <si>
+    <t>2025-04-14 14:08:23</t>
+  </si>
+  <si>
+    <t>0:12:54</t>
+  </si>
+  <si>
+    <t>2025-04-14 14:39:55</t>
+  </si>
+  <si>
+    <t>0:17:59</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.8_Den_10%_Noz_1.0_Tim_000644.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 14:52:01</t>
+  </si>
+  <si>
+    <t>0:10:34</t>
+  </si>
+  <si>
+    <t>2025-04-14 15:03:51</t>
+  </si>
+  <si>
+    <t>0:10:59</t>
+  </si>
+  <si>
+    <t>2025-04-14 15:39:01</t>
+  </si>
+  <si>
+    <t>0:08:17</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.1_Den_10%_Noz_1.0_Tim_005341.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 15:53:04</t>
+  </si>
+  <si>
+    <t>0:09:17</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.1_Den_10%_Noz_1.0_Tim_003655.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 16:02:52</t>
+  </si>
+  <si>
+    <t>2025-04-14 16:08:07</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.8_Den_10%_Noz_1.0_Tim_000704.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 16:18:21</t>
+  </si>
+  <si>
+    <t>0:06:43</t>
+  </si>
+  <si>
+    <t>2025-04-14 16:29:21</t>
+  </si>
+  <si>
+    <t>0:10:50</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.1_Den_10%_Noz_1.0_Tim_003715.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 17:13:53</t>
+  </si>
+  <si>
+    <t>0:42:15</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001216.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 18:21:41</t>
+  </si>
+  <si>
+    <t>0:18:19</t>
+  </si>
+  <si>
+    <t>2025-04-14 18:40:00</t>
+  </si>
+  <si>
+    <t>0:13:00</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:05:30</t>
+  </si>
+  <si>
+    <t>0:12:43</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001539.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:21:44</t>
+  </si>
+  <si>
+    <t>0:09:43</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:28:37</t>
+  </si>
+  <si>
+    <t>0:06:23</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001623.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:36:28</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:56:13</t>
+  </si>
+  <si>
+    <t>0:18:59</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001314.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 20:45:05</t>
+  </si>
+  <si>
+    <t>0:08:53</t>
+  </si>
+  <si>
+    <t>2025-04-14 20:56:56</t>
+  </si>
+  <si>
+    <t>0:11:25</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001355.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:00:55</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:03:32</t>
+  </si>
+  <si>
+    <t>0:01:38</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:11:22</t>
+  </si>
+  <si>
+    <t>0:07:04</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001409.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:19:46</t>
+  </si>
+  <si>
+    <t>0:05:26</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:23:37</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:27:22</t>
+  </si>
+  <si>
+    <t>0:03:02</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:29:37</t>
+  </si>
+  <si>
+    <t>0:01:34</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:31:47</t>
+  </si>
+  <si>
+    <t>0:01:32</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:44:52</t>
+  </si>
+  <si>
+    <t>0:12:25</t>
+  </si>
+  <si>
+    <t>2025-04-14 21:58:41</t>
+  </si>
+  <si>
+    <t>0:13:39</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.1_Den_10%_Noz_1.0_Tim_005509.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-14 22:57:30</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.1_Den_10%_Noz_1.0_Tim_043249.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 03:33:07</t>
+  </si>
+  <si>
+    <t>4:31:59</t>
+  </si>
+  <si>
+    <t>2025-04-15 07:34:19</t>
+  </si>
+  <si>
+    <t>1:05:59</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.8_Den_10%_Noz_1.0_Tim_004511.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 09:18:08</t>
+  </si>
+  <si>
+    <t>0:29:40</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.5_Den_10%_Noz_1.0_Tim_001606.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 09:29:19</t>
+  </si>
+  <si>
+    <t>2025-04-15 09:50:00</t>
+  </si>
+  <si>
+    <t>0:20:10</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.5_Den_10%_Noz_1.0_Tim_010252.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 10:52:58</t>
+  </si>
+  <si>
+    <t>1:02:28</t>
+  </si>
+  <si>
+    <t>2025-04-15 12:26:40</t>
+  </si>
+  <si>
+    <t>0:17:49</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.1_Den_10%_Noz_1.0_Tim_005747.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 21:52:22</t>
+  </si>
+  <si>
+    <t>0:18:56</t>
+  </si>
+  <si>
+    <t>2025-04-15 22:02:09</t>
+  </si>
+  <si>
+    <t>0:09:09</t>
+  </si>
+  <si>
+    <t>2025-04-15 22:18:58</t>
+  </si>
+  <si>
+    <t>0:14:41</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.1_Den_10%_Noz_1.0_Tim_005941.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 22:49:58</t>
+  </si>
+  <si>
+    <t>0:03:18</t>
+  </si>
+  <si>
+    <t>2025-04-15 22:56:31</t>
+  </si>
+  <si>
+    <t>0:06:07</t>
+  </si>
+  <si>
+    <t>2025-04-15 23:01:26</t>
+  </si>
+  <si>
+    <t>0:03:33</t>
+  </si>
+  <si>
+    <t>2025-04-15 23:06:23</t>
+  </si>
+  <si>
+    <t>0:04:46</t>
+  </si>
+  <si>
+    <t>2025-04-15 23:10:05</t>
+  </si>
+  <si>
+    <t>0:02:58</t>
+  </si>
+  <si>
+    <t>2025-04-15 23:29:41</t>
+  </si>
+  <si>
+    <t>0:18:58</t>
+  </si>
+  <si>
+    <t>ABS_sharkz_Res_0.8_Den_10%_Noz_1.0_Tim_001604.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-15 23:45:32</t>
+  </si>
+  <si>
+    <t>0:10:52</t>
+  </si>
+  <si>
+    <t>2025-04-16 00:06:18</t>
+  </si>
+  <si>
+    <t>0:17:10</t>
+  </si>
+  <si>
+    <t>2025-04-16 00:28:57</t>
+  </si>
+  <si>
+    <t>ABS_wildrosebuilds_puzzlecube_Res_0.1_Den_10%_Noz_1.0_Tim_021823.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 03:27:48</t>
+  </si>
+  <si>
+    <t>ABS_wildrosebuilds_puzzlecube_Res_0.5_Den_10%_Noz_1.0_Tim_003834.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 05:09:06</t>
+  </si>
+  <si>
+    <t>0:47:07</t>
+  </si>
+  <si>
+    <t>ABS_wildrosebuilds_puzzlecube_Res_0.8_Den_10%_Noz_1.0_Tim_002852.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 07:19:30</t>
+  </si>
+  <si>
+    <t>0:38:07</t>
+  </si>
+  <si>
+    <t>2025-04-16 11:25:10</t>
+  </si>
+  <si>
+    <t>0:23:30</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.8_Den_10%_Noz_1.0_Tim_004313.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 12:11:32</t>
+  </si>
+  <si>
+    <t>0:44:07</t>
+  </si>
+  <si>
+    <t>ABS_Octopus_spiral_sup_v6_Res_0.1_Den_10%_Noz_1.0_Tim_025210.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 15:48:24</t>
+  </si>
+  <si>
+    <t>2:53:10</t>
+  </si>
+  <si>
+    <t>ABS_Octopus_spiral_sup_v6_Res_0.5_Den_10%_Noz_1.0_Tim_004804.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 17:04:11</t>
+  </si>
+  <si>
+    <t>2025-04-16 17:30:54</t>
+  </si>
+  <si>
+    <t>0:26:14</t>
+  </si>
+  <si>
+    <t>2025-04-16 19:16:29</t>
+  </si>
+  <si>
+    <t>0:56:24</t>
+  </si>
+  <si>
+    <t>ABS_Octopus_spiral_sup_v6_Res_0.8_Den_20%_Noz_1.0_Tim_003706.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-16 20:21:20</t>
+  </si>
+  <si>
+    <t>0:44:06</t>
+  </si>
+  <si>
+    <t>2025-04-16 21:10:55</t>
+  </si>
+  <si>
+    <t>0:45:05</t>
+  </si>
+  <si>
+    <t>ABS_Ball_Bearing.A.3_Res_0.8_Den_10%_Noz_1.0_Tim_004256.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-17 21:22:34</t>
+  </si>
+  <si>
+    <t>ABS_3D_Printer_test_fixed_stl_3rd_gen_Res_0.1_Den_20%_Noz_1.0_Tim_044626.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-18 21:22:12</t>
+  </si>
+  <si>
+    <t>4:49:10</t>
+  </si>
+  <si>
+    <t>ABS_Ball_Bearing.A.3_Res_0.1_Den_20%_Noz_1.0_Tim_034154.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-19 01:55:09</t>
+  </si>
+  <si>
+    <t>3:46:41</t>
+  </si>
+  <si>
+    <t>ABS_Ball_Bearing.A.3_Res_0.5_Den_20%_Noz_1.0_Tim_010108.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-19 17:59:18</t>
+  </si>
+  <si>
+    <t>1:09:00</t>
+  </si>
+  <si>
+    <t>ABS_Ball_Bearing.A.3_Res_0.8_Den_20%_Noz_1.0_Tim_004833.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-19 19:31:07</t>
+  </si>
+  <si>
+    <t>0:54:01</t>
+  </si>
+  <si>
+    <t>ABS_VaseDoubleTwist_Res_0.7_Den_20%_Noz_1.0_Tim_005505.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-19 21:03:58</t>
+  </si>
+  <si>
+    <t>0:58:59</t>
+  </si>
+  <si>
+    <t>ABS_peristaltic_Res_0.1_Den_20%_Noz_1.0_Tim_022438.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-19 23:49:59</t>
+  </si>
+  <si>
+    <t>2:30:06</t>
+  </si>
+  <si>
+    <t>ABS_peristaltic_Res_0.5_Den_20%_Noz_1.0_Tim_004301.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-20 00:37:00</t>
+  </si>
+  <si>
+    <t>0:45:45</t>
+  </si>
+  <si>
+    <t>ABS_peristaltic_Res_0.8_Den_20%_Noz_1.0_Tim_003320.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-20 01:20:18</t>
+  </si>
+  <si>
+    <t>0:37:56</t>
+  </si>
+  <si>
+    <t>2025-04-20 18:52:36</t>
+  </si>
+  <si>
+    <t>4:31:14</t>
+  </si>
+  <si>
+    <t>ABS_xyzCalibration_cube_Res_0.1_Den_10%_Noz_0.6_Tim_005123.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-20 19:29:41</t>
+  </si>
+  <si>
+    <t>2025-04-20 19:37:48</t>
+  </si>
+  <si>
+    <t>0:05:16</t>
+  </si>
+  <si>
+    <t>2025-04-20 20:33:21</t>
+  </si>
+  <si>
+    <t>0:54:52</t>
+  </si>
+  <si>
+    <t>2025-04-20 21:29:48</t>
+  </si>
+  <si>
+    <t>0:55:08</t>
+  </si>
+  <si>
+    <t>ABS_Nozzle_holder_small_Res_0.3_Den_15%_Noz_0.6_Tim_014306.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-20 23:20:14</t>
+  </si>
+  <si>
+    <t>1:42:54</t>
+  </si>
+  <si>
+    <t>ABS_Nozzle_holder_small_Res_0.1_Den_15%_Noz_0.6_Tim_040358.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-21 04:04:28</t>
+  </si>
+  <si>
+    <t>4:03:56</t>
+  </si>
+  <si>
+    <t>2025-04-21 11:29:42</t>
+  </si>
+  <si>
+    <t>4:09:11</t>
+  </si>
+  <si>
+    <t>2025-04-21 16:26:56</t>
+  </si>
+  <si>
+    <t>4:08:21</t>
+  </si>
+  <si>
+    <t>2025-04-22 00:55:21</t>
+  </si>
+  <si>
+    <t>4:09:07</t>
+  </si>
+  <si>
+    <t>2025-04-22 05:43:04</t>
+  </si>
+  <si>
+    <t>4:08:23</t>
+  </si>
+  <si>
+    <t>2025-04-22 11:49:52</t>
+  </si>
+  <si>
+    <t>4:09:05</t>
+  </si>
+  <si>
+    <t>2025-04-22 20:02:58</t>
+  </si>
+  <si>
+    <t>4:09:16</t>
+  </si>
+  <si>
+    <t>ABS_cable_organizer_1S_Res_0.1_Den_10%_Noz_0.6_Tim_085755.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-22 23:42:44</t>
+  </si>
+  <si>
+    <t>0:02:34</t>
+  </si>
+  <si>
+    <t>ABS_cable_organizer_1S_Res_0.1_Den_10%_Noz_0.6_Tim_090735.gcode</t>
+  </si>
+  <si>
+    <t>2025-04-23 08:48:30</t>
+  </si>
+  <si>
+    <t>9:03:33</t>
+  </si>
+  <si>
+    <t>2025-04-23 16:10:59</t>
+  </si>
+  <si>
+    <t>4:09:10</t>
   </si>
 </sst>
 </file>
@@ -3417,7 +4122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H446"/>
+  <dimension ref="A1:H545"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -12346,6 +13051,1986 @@
         <v>0</v>
       </c>
     </row>
+    <row r="447" spans="1:7">
+      <c r="A447" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F447">
+        <v>14436.18167000044</v>
+      </c>
+      <c r="G447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
+      <c r="A448" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+      <c r="D448" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F448">
+        <v>0</v>
+      </c>
+      <c r="G448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="A449" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F449">
+        <v>12800.49955999991</v>
+      </c>
+      <c r="G449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
+      <c r="A450" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+      <c r="D450" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F450">
+        <v>8750.019340000164</v>
+      </c>
+      <c r="G450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F451">
+        <v>14317.40261999997</v>
+      </c>
+      <c r="G451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
+      <c r="A452" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F452">
+        <v>11662.52032000018</v>
+      </c>
+      <c r="G452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
+      <c r="A453" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
+      </c>
+      <c r="D453" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F453">
+        <v>3077.826489999999</v>
+      </c>
+      <c r="G453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F454">
+        <v>15929.34248000006</v>
+      </c>
+      <c r="G454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
+      <c r="A455" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F455">
+        <v>12151.04150000002</v>
+      </c>
+      <c r="G455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
+      <c r="A456" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F456">
+        <v>12151.04150000002</v>
+      </c>
+      <c r="G456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
+      <c r="A457" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F457">
+        <v>10911.7741200027</v>
+      </c>
+      <c r="G457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
+      <c r="A458" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F458">
+        <v>12151.04150000002</v>
+      </c>
+      <c r="G458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459" t="s">
+        <v>757</v>
+      </c>
+      <c r="F459">
+        <v>0</v>
+      </c>
+      <c r="G459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
+      <c r="A460" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F460">
+        <v>1227.403290000001</v>
+      </c>
+      <c r="G460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
+      <c r="A461" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F461">
+        <v>1227.403290000001</v>
+      </c>
+      <c r="G461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F462">
+        <v>1445.464550000001</v>
+      </c>
+      <c r="G462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
+      <c r="A463" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F463">
+        <v>1445.464550000001</v>
+      </c>
+      <c r="G463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
+      <c r="A464" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F464">
+        <v>1445.464550000001</v>
+      </c>
+      <c r="G464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7">
+      <c r="A465" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F465">
+        <v>2216.782980000001</v>
+      </c>
+      <c r="G465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7">
+      <c r="A466" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466" t="s">
+        <v>441</v>
+      </c>
+      <c r="F466">
+        <v>956.5370899999986</v>
+      </c>
+      <c r="G466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7">
+      <c r="A467" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F467">
+        <v>956.5370899999986</v>
+      </c>
+      <c r="G467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7">
+      <c r="A468" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F468">
+        <v>1509.022899999999</v>
+      </c>
+      <c r="G468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7">
+      <c r="A469" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F469">
+        <v>1509.022899999999</v>
+      </c>
+      <c r="G469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7">
+      <c r="A470" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F470">
+        <v>972.5212299999993</v>
+      </c>
+      <c r="G470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7">
+      <c r="A471" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F471">
+        <v>3069.619040000001</v>
+      </c>
+      <c r="G471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7">
+      <c r="A472" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F472">
+        <v>3069.619040000001</v>
+      </c>
+      <c r="G472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7">
+      <c r="A473" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F473">
+        <v>3069.619040000001</v>
+      </c>
+      <c r="G473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7">
+      <c r="A474" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F474">
+        <v>4598.798949999997</v>
+      </c>
+      <c r="G474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7">
+      <c r="A475" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F475">
+        <v>4598.798949999997</v>
+      </c>
+      <c r="G475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7">
+      <c r="A476" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476" t="s">
+        <v>161</v>
+      </c>
+      <c r="F476">
+        <v>4408.589239999992</v>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7">
+      <c r="A477" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F477">
+        <v>4408.589239999992</v>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7">
+      <c r="A478" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F478">
+        <v>3299.108030000002</v>
+      </c>
+      <c r="G478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7">
+      <c r="A479" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F479">
+        <v>3299.108030000002</v>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7">
+      <c r="A480" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480" t="s">
+        <v>336</v>
+      </c>
+      <c r="F480">
+        <v>3348.567509999999</v>
+      </c>
+      <c r="G480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7">
+      <c r="A481" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F481">
+        <v>3348.567509999999</v>
+      </c>
+      <c r="G481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7">
+      <c r="A482" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+      <c r="D482" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F482">
+        <v>3348.567509999999</v>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7">
+      <c r="A483" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+      <c r="D483" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F483">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7">
+      <c r="A484" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+      <c r="D484" t="s">
+        <v>250</v>
+      </c>
+      <c r="F484">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7">
+      <c r="A485" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+      <c r="D485" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F485">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7">
+      <c r="A486" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+      <c r="D486" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F486">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7">
+      <c r="A487" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+      <c r="D487" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F487">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7">
+      <c r="A488" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+      <c r="D488" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F488">
+        <v>3177.623839999998</v>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7">
+      <c r="A489" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+      <c r="D489" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F489">
+        <v>3069.629380000001</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7">
+      <c r="A490" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+      <c r="D490" t="s">
+        <v>865</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7">
+      <c r="A491" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+      <c r="D491" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F491">
+        <v>15330.37602999979</v>
+      </c>
+      <c r="G491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7">
+      <c r="A492" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+      <c r="D492" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F492">
+        <v>2287.090200000015</v>
+      </c>
+      <c r="G492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7">
+      <c r="A493" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+      <c r="D493" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F493">
+        <v>16726.29184000004</v>
+      </c>
+      <c r="G493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7">
+      <c r="A494" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+      <c r="D494" t="s">
+        <v>968</v>
+      </c>
+      <c r="F494">
+        <v>2650.74765</v>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7">
+      <c r="A495" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F495">
+        <v>2650.74765</v>
+      </c>
+      <c r="G495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7">
+      <c r="A496" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F496">
+        <v>15929.34151000007</v>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7">
+      <c r="A497" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+      <c r="D497" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F497">
+        <v>3069.629380000001</v>
+      </c>
+      <c r="G497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7">
+      <c r="A498" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F498">
+        <v>2704.625460000006</v>
+      </c>
+      <c r="G498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7">
+      <c r="A499" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+      <c r="D499" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F499">
+        <v>2704.625460000006</v>
+      </c>
+      <c r="G499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7">
+      <c r="A500" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+      <c r="D500" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F500">
+        <v>2704.625460000006</v>
+      </c>
+      <c r="G500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7">
+      <c r="A501" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C501">
+        <v>0</v>
+      </c>
+      <c r="D501" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F501">
+        <v>0</v>
+      </c>
+      <c r="G501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7">
+      <c r="A502" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C502">
+        <v>0</v>
+      </c>
+      <c r="D502" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F502">
+        <v>3002.099420000001</v>
+      </c>
+      <c r="G502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7">
+      <c r="A503" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C503">
+        <v>0</v>
+      </c>
+      <c r="D503" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F503">
+        <v>3002.099420000001</v>
+      </c>
+      <c r="G503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7">
+      <c r="A504" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C504">
+        <v>0</v>
+      </c>
+      <c r="D504" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F504">
+        <v>3002.099420000001</v>
+      </c>
+      <c r="G504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7">
+      <c r="A505" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C505">
+        <v>0</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F505">
+        <v>3002.099420000001</v>
+      </c>
+      <c r="G505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7">
+      <c r="A506" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C506">
+        <v>0</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F506">
+        <v>3002.099420000001</v>
+      </c>
+      <c r="G506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7">
+      <c r="A507" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C507">
+        <v>0</v>
+      </c>
+      <c r="D507" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F507">
+        <v>3475.263970000002</v>
+      </c>
+      <c r="G507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7">
+      <c r="A508" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+      <c r="D508" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F508">
+        <v>3475.263970000002</v>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7">
+      <c r="A509" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+      <c r="D509" t="s">
+        <v>169</v>
+      </c>
+      <c r="F509">
+        <v>3475.263970000002</v>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7">
+      <c r="A510" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510" t="s">
+        <v>657</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7">
+      <c r="A511" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F511">
+        <v>5872.080760000004</v>
+      </c>
+      <c r="G511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7">
+      <c r="A512" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F512">
+        <v>6136.381110000005</v>
+      </c>
+      <c r="G512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7">
+      <c r="A513" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F513">
+        <v>0</v>
+      </c>
+      <c r="G513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7">
+      <c r="A514" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F514">
+        <v>0</v>
+      </c>
+      <c r="G514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7">
+      <c r="A515" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F515">
+        <v>0</v>
+      </c>
+      <c r="G515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7">
+      <c r="A516" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C516">
+        <v>0</v>
+      </c>
+      <c r="D516" t="s">
+        <v>382</v>
+      </c>
+      <c r="F516">
+        <v>6716.901360000052</v>
+      </c>
+      <c r="G516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7">
+      <c r="A517" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C517">
+        <v>0</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F517">
+        <v>6716.901360000052</v>
+      </c>
+      <c r="G517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7">
+      <c r="A518" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F518">
+        <v>6716.901360000052</v>
+      </c>
+      <c r="G518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7">
+      <c r="A519" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F519">
+        <v>0</v>
+      </c>
+      <c r="G519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7">
+      <c r="A520" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+      <c r="D520" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F520">
+        <v>16226.19395999984</v>
+      </c>
+      <c r="G520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7">
+      <c r="A521" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521" t="s">
+        <v>585</v>
+      </c>
+      <c r="F521">
+        <v>0</v>
+      </c>
+      <c r="G521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7">
+      <c r="A522" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F522">
+        <v>0</v>
+      </c>
+      <c r="G522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7">
+      <c r="A523" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F523">
+        <v>9729.522719999988</v>
+      </c>
+      <c r="G523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7">
+      <c r="A524" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7">
+      <c r="A525" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F525">
+        <v>0</v>
+      </c>
+      <c r="G525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7">
+      <c r="A526" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F526">
+        <v>0</v>
+      </c>
+      <c r="G526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7">
+      <c r="A527" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F527">
+        <v>0</v>
+      </c>
+      <c r="G527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7">
+      <c r="A528" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+      <c r="D528" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F528">
+        <v>7104.602910000032</v>
+      </c>
+      <c r="G528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7">
+      <c r="A529" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F529">
+        <v>0</v>
+      </c>
+      <c r="G529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7">
+      <c r="A530" t="s">
+        <v>979</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F530">
+        <v>15330.37602999979</v>
+      </c>
+      <c r="G530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7">
+      <c r="A531" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C531">
+        <v>0</v>
+      </c>
+      <c r="D531" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F531">
+        <v>1434.615579999998</v>
+      </c>
+      <c r="G531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7">
+      <c r="A532" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C532">
+        <v>0</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F532">
+        <v>1434.615579999998</v>
+      </c>
+      <c r="G532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7">
+      <c r="A533" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C533">
+        <v>1</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F533">
+        <v>1434.615579999998</v>
+      </c>
+      <c r="G533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7">
+      <c r="A534" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F534">
+        <v>1434.615579999998</v>
+      </c>
+      <c r="G534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7">
+      <c r="A535" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C535">
+        <v>1</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F535">
+        <v>0</v>
+      </c>
+      <c r="G535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7">
+      <c r="A536" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F536">
+        <v>0</v>
+      </c>
+      <c r="G536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7">
+      <c r="A537" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C537">
+        <v>1</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F537">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7">
+      <c r="A538" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C538">
+        <v>1</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F538">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7">
+      <c r="A539" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C539">
+        <v>1</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F539">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7">
+      <c r="A540" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C540">
+        <v>1</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F540">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7">
+      <c r="A541" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C541">
+        <v>1</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F541">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7">
+      <c r="A542" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C542">
+        <v>1</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F542">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7">
+      <c r="A543" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C543">
+        <v>0</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F543">
+        <v>0</v>
+      </c>
+      <c r="G543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7">
+      <c r="A544" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C544">
+        <v>1</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F544">
+        <v>0</v>
+      </c>
+      <c r="G544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7">
+      <c r="A545" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C545">
+        <v>1</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F545">
+        <v>7063.273789999839</v>
+      </c>
+      <c r="G545">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
